--- a/outputs/Block2_Module_Contract_v12.xlsx
+++ b/outputs/Block2_Module_Contract_v12.xlsx
@@ -31,7 +31,7 @@
     <t>May Not Mutate</t>
   </si>
   <si>
-    <t>National 42-target engine</t>
+    <t>National DPP/RPP engine</t>
   </si>
   <si>
     <t>Popular-vote selector</t>
@@ -40,7 +40,7 @@
     <t>State Senate model</t>
   </si>
   <si>
-    <t>71 pre-election features</t>
+    <t>42 production pre-election features</t>
   </si>
   <si>
     <t>EDPP, ERPP; historical DPP/RPP for sealed validation</t>
@@ -49,7 +49,7 @@
     <t>Frozen national signals + Senate Parser/Historic</t>
   </si>
   <si>
-    <t>34 learned targets + 8 deterministic identities</t>
+    <t>2 learned national outcomes + 8 downstream compatibility placeholders</t>
   </si>
   <si>
     <t>DPP, RPP and residual Other</t>
@@ -64,7 +64,7 @@
     <t>National pre-election expectation</t>
   </si>
   <si>
-    <t>National vote and Senate-bucket signals</t>
+    <t>Frozen national popular-vote signal + Senate Parser/Senate Historic; HIST SENATE RESULTS for realized-outcome reconciliation only</t>
   </si>
   <si>
     <t>Source inputs</t>
@@ -73,7 +73,7 @@
     <t>House targets; Senate targets; state Senate data</t>
   </si>
   <si>
-    <t>Any of the 42 national targets</t>
+    <t>DPP/RPP or any race-first chamber winner</t>
   </si>
 </sst>
 </file>
